--- a/data/nzd0165/nzd0165.xlsx
+++ b/data/nzd0165/nzd0165.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H375"/>
+  <dimension ref="A1:H376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11688,6 +11688,36 @@
         <v>405.78</v>
       </c>
       <c r="H375" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>430.76</v>
+      </c>
+      <c r="C376" t="n">
+        <v>403.06</v>
+      </c>
+      <c r="D376" t="n">
+        <v>404.18</v>
+      </c>
+      <c r="E376" t="n">
+        <v>402.72</v>
+      </c>
+      <c r="F376" t="n">
+        <v>400.48</v>
+      </c>
+      <c r="G376" t="n">
+        <v>404.63</v>
+      </c>
+      <c r="H376" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11704,7 +11734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B400"/>
+  <dimension ref="A1:B401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15707,6 +15737,16 @@
       </c>
       <c r="B400" t="n">
         <v>0.65</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -15875,28 +15915,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07223593750654636</v>
+        <v>0.07312537678468013</v>
       </c>
       <c r="J2" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K2" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009506672042149278</v>
+        <v>0.009794814461159151</v>
       </c>
       <c r="M2" t="n">
-        <v>4.178626409488131</v>
+        <v>4.171790067343694</v>
       </c>
       <c r="N2" t="n">
-        <v>28.25955343323489</v>
+        <v>28.19114156667265</v>
       </c>
       <c r="O2" t="n">
-        <v>5.315971541800698</v>
+        <v>5.309533083678136</v>
       </c>
       <c r="P2" t="n">
-        <v>427.2508256276727</v>
+        <v>427.2414122538074</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -15957,28 +15997,28 @@
         <v>0.0638</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02313761639288605</v>
+        <v>0.02071745766587047</v>
       </c>
       <c r="J3" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K3" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001250790395829537</v>
+        <v>0.001006679082742434</v>
       </c>
       <c r="M3" t="n">
-        <v>3.873142505805693</v>
+        <v>3.876099082775907</v>
       </c>
       <c r="N3" t="n">
-        <v>22.22003653974143</v>
+        <v>22.21221693151534</v>
       </c>
       <c r="O3" t="n">
-        <v>4.713813375574115</v>
+        <v>4.712983867096867</v>
       </c>
       <c r="P3" t="n">
-        <v>406.8634133673763</v>
+        <v>406.8890270989383</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -16039,28 +16079,28 @@
         <v>0.0733</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008614541623935377</v>
+        <v>0.006983917662879844</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K4" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002442629605270419</v>
+        <v>0.0001612707175188133</v>
       </c>
       <c r="M4" t="n">
-        <v>3.236472030392907</v>
+        <v>3.237134722504542</v>
       </c>
       <c r="N4" t="n">
-        <v>15.78833239336699</v>
+        <v>15.76957919816197</v>
       </c>
       <c r="O4" t="n">
-        <v>3.973453459318102</v>
+        <v>3.971092947560151</v>
       </c>
       <c r="P4" t="n">
-        <v>406.9296302261166</v>
+        <v>406.9468879224613</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -16121,28 +16161,28 @@
         <v>0.0835</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01672222384876127</v>
+        <v>-0.0177244883877355</v>
       </c>
       <c r="J5" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K5" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0008882553185604047</v>
+        <v>0.001003191416194427</v>
       </c>
       <c r="M5" t="n">
-        <v>3.14271439723576</v>
+        <v>3.139449835751359</v>
       </c>
       <c r="N5" t="n">
-        <v>16.34932918332628</v>
+        <v>16.31455213485028</v>
       </c>
       <c r="O5" t="n">
-        <v>4.043430373250698</v>
+        <v>4.039127645278159</v>
       </c>
       <c r="P5" t="n">
-        <v>404.9862878654686</v>
+        <v>404.9968953246276</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -16203,28 +16243,28 @@
         <v>0.0956</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09571487347333449</v>
+        <v>-0.09660480624108507</v>
       </c>
       <c r="J6" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K6" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02611841545249316</v>
+        <v>0.02673686712620282</v>
       </c>
       <c r="M6" t="n">
-        <v>3.257954165517973</v>
+        <v>3.25436351163084</v>
       </c>
       <c r="N6" t="n">
-        <v>17.75635471413766</v>
+        <v>17.71595908840748</v>
       </c>
       <c r="O6" t="n">
-        <v>4.213828984918309</v>
+        <v>4.209033034843928</v>
       </c>
       <c r="P6" t="n">
-        <v>404.6091079761091</v>
+        <v>404.618526572818</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -16285,28 +16325,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09956187527423009</v>
+        <v>-0.1029687803882467</v>
       </c>
       <c r="J7" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K7" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02894579381717377</v>
+        <v>0.03089920341864005</v>
       </c>
       <c r="M7" t="n">
-        <v>3.432885975295659</v>
+        <v>3.439683201148891</v>
       </c>
       <c r="N7" t="n">
-        <v>17.28541340249656</v>
+        <v>17.34124407419958</v>
       </c>
       <c r="O7" t="n">
-        <v>4.157573018300046</v>
+        <v>4.164281939806619</v>
       </c>
       <c r="P7" t="n">
-        <v>413.4429199285493</v>
+        <v>413.4789768830263</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -16348,7 +16388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H375"/>
+  <dimension ref="A1:H376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32101,6 +32141,48 @@
         </is>
       </c>
     </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>-36.76441103411335,175.1446578011967</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>-36.76468540625733,175.14543921123717</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>-36.764496419422336,175.14617412949366</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>-36.76419811965612,175.14689933027032</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>-36.76381666138257,175.14761157048028</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>-36.76334711279676,175.1482783729432</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0165/nzd0165.xlsx
+++ b/data/nzd0165/nzd0165.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H376"/>
+  <dimension ref="A1:H377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11718,6 +11718,36 @@
         <v>404.63</v>
       </c>
       <c r="H376" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>419.48</v>
+      </c>
+      <c r="C377" t="n">
+        <v>403.18</v>
+      </c>
+      <c r="D377" t="n">
+        <v>404.21</v>
+      </c>
+      <c r="E377" t="n">
+        <v>402.69</v>
+      </c>
+      <c r="F377" t="n">
+        <v>402.3</v>
+      </c>
+      <c r="G377" t="n">
+        <v>407.57</v>
+      </c>
+      <c r="H377" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11734,7 +11764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B401"/>
+  <dimension ref="A1:B402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15747,6 +15777,16 @@
       </c>
       <c r="B401" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>-0.19</v>
       </c>
     </row>
   </sheetData>
@@ -15915,34 +15955,30 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07312537678468013</v>
+        <v>0.06781549874016352</v>
       </c>
       <c r="J2" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K2" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009794814461159151</v>
+        <v>0.008412152992821165</v>
       </c>
       <c r="M2" t="n">
-        <v>4.171790067343694</v>
+        <v>4.186539471642756</v>
       </c>
       <c r="N2" t="n">
-        <v>28.19114156667265</v>
+        <v>28.36332769039447</v>
       </c>
       <c r="O2" t="n">
-        <v>5.309533083678136</v>
+        <v>5.325723208203227</v>
       </c>
       <c r="P2" t="n">
-        <v>427.2414122538074</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>427.2978182982827</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>LINESTRING (175.14459555594647 -36.768292166996076, 175.14472841536596 -36.76000834294725)</t>
@@ -15997,34 +16033,30 @@
         <v>0.0638</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02071745766587047</v>
+        <v>0.01838379346503206</v>
       </c>
       <c r="J3" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K3" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001006679082742434</v>
+        <v>0.0007958468128147489</v>
       </c>
       <c r="M3" t="n">
-        <v>3.876099082775907</v>
+        <v>3.878474063571339</v>
       </c>
       <c r="N3" t="n">
-        <v>22.21221693151534</v>
+        <v>22.20088275626715</v>
       </c>
       <c r="O3" t="n">
-        <v>4.712983867096867</v>
+        <v>4.711781272116433</v>
       </c>
       <c r="P3" t="n">
-        <v>406.8890270989383</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>406.9138172665465</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>LINESTRING (175.1461242943557 -36.76827519549791, 175.14456163180967 -36.76008638554916)</t>
@@ -16079,34 +16111,30 @@
         <v>0.0733</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006983917662879844</v>
+        <v>0.005384505530800342</v>
       </c>
       <c r="J4" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K4" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001612707175188133</v>
+        <v>9.630364774537714e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.237134722504542</v>
+        <v>3.237549845448654</v>
       </c>
       <c r="N4" t="n">
-        <v>15.76957919816197</v>
+        <v>15.75006392705328</v>
       </c>
       <c r="O4" t="n">
-        <v>3.971092947560151</v>
+        <v>3.968635020640382</v>
       </c>
       <c r="P4" t="n">
-        <v>406.9468879224613</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>406.9638782395835</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>LINESTRING (175.14798547498552 -36.76783408439462, 175.1438644036373 -36.76023993115124)</t>
@@ -16161,34 +16189,30 @@
         <v>0.0835</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0177244883877355</v>
+        <v>-0.0187371405995635</v>
       </c>
       <c r="J5" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K5" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001003191416194427</v>
+        <v>0.001127025319579977</v>
       </c>
       <c r="M5" t="n">
-        <v>3.139449835751359</v>
+        <v>3.136282266177778</v>
       </c>
       <c r="N5" t="n">
-        <v>16.31455213485028</v>
+        <v>16.28015184149083</v>
       </c>
       <c r="O5" t="n">
-        <v>4.039127645278159</v>
+        <v>4.034867016580699</v>
       </c>
       <c r="P5" t="n">
-        <v>404.9968953246276</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>405.0076525784138</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>LINESTRING (175.1493484343171 -36.76724533105793, 175.14375501003147 -36.760285464396404)</t>
@@ -16243,34 +16267,30 @@
         <v>0.0956</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09660480624108507</v>
+        <v>-0.09648362459403864</v>
       </c>
       <c r="J6" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K6" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02673686712620282</v>
+        <v>0.02682634695007957</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25436351163084</v>
+        <v>3.246185991751274</v>
       </c>
       <c r="N6" t="n">
-        <v>17.71595908840748</v>
+        <v>17.6689709081708</v>
       </c>
       <c r="O6" t="n">
-        <v>4.209033034843928</v>
+        <v>4.203447502725686</v>
       </c>
       <c r="P6" t="n">
-        <v>404.618526572818</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>404.6172392782105</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>LINESTRING (175.15036155760768 -36.766667407450306, 175.14404503047072 -36.760119019720115)</t>
@@ -16325,34 +16345,30 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1029687803882467</v>
+        <v>-0.1047264557680361</v>
       </c>
       <c r="J7" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K7" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03089920341864005</v>
+        <v>0.03206498448987183</v>
       </c>
       <c r="M7" t="n">
-        <v>3.439683201148891</v>
+        <v>3.438753556443084</v>
       </c>
       <c r="N7" t="n">
-        <v>17.34124407419958</v>
+        <v>17.32220638054403</v>
       </c>
       <c r="O7" t="n">
-        <v>4.164281939806619</v>
+        <v>4.161995480601106</v>
       </c>
       <c r="P7" t="n">
-        <v>413.4789768830263</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>413.4976484070829</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>LINESTRING (175.15114359255713 -36.76617184513378, 175.14462962822878 -36.75974951266995)</t>
@@ -16388,7 +16404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H376"/>
+  <dimension ref="A1:H377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32183,6 +32199,48 @@
         </is>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>-36.764512666555866,175.1446561711806</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>-36.76468433749539,175.14543900728333</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>-36.76449617168502,175.14617399505377</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>-36.764198346655576,175.14689951270515</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>-36.76380370587116,175.1475990735057</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>-36.76332658829959,175.14825755532806</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0165/nzd0165.xlsx
+++ b/data/nzd0165/nzd0165.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H377"/>
+  <dimension ref="A1:H379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11750,6 +11750,66 @@
       <c r="H377" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>429.92</v>
+      </c>
+      <c r="C378" t="n">
+        <v>403.21</v>
+      </c>
+      <c r="D378" t="n">
+        <v>405.23</v>
+      </c>
+      <c r="E378" t="n">
+        <v>404.01</v>
+      </c>
+      <c r="F378" t="n">
+        <v>400.12</v>
+      </c>
+      <c r="G378" t="n">
+        <v>406.09</v>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:33+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>429.92</v>
+      </c>
+      <c r="C379" t="n">
+        <v>405.87</v>
+      </c>
+      <c r="D379" t="n">
+        <v>407.66</v>
+      </c>
+      <c r="E379" t="n">
+        <v>406.96</v>
+      </c>
+      <c r="F379" t="n">
+        <v>401.9</v>
+      </c>
+      <c r="G379" t="n">
+        <v>409.12</v>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11764,7 +11824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B402"/>
+  <dimension ref="A1:B404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15787,6 +15847,26 @@
       </c>
       <c r="B402" t="n">
         <v>-0.19</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>
@@ -15955,28 +16035,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06781549874016352</v>
+        <v>0.06872332554069469</v>
       </c>
       <c r="J2" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K2" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008412152992821165</v>
+        <v>0.00873803109124105</v>
       </c>
       <c r="M2" t="n">
-        <v>4.186539471642756</v>
+        <v>4.168686167600943</v>
       </c>
       <c r="N2" t="n">
-        <v>28.36332769039447</v>
+        <v>28.21689252068242</v>
       </c>
       <c r="O2" t="n">
-        <v>5.325723208203227</v>
+        <v>5.311957503659307</v>
       </c>
       <c r="P2" t="n">
-        <v>427.2978182982827</v>
+        <v>427.2881435665606</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16033,28 +16113,28 @@
         <v>0.0638</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01838379346503206</v>
+        <v>0.015284772461906</v>
       </c>
       <c r="J3" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K3" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007958468128147489</v>
+        <v>0.0005555435833860534</v>
       </c>
       <c r="M3" t="n">
-        <v>3.878474063571339</v>
+        <v>3.874622838800041</v>
       </c>
       <c r="N3" t="n">
-        <v>22.20088275626715</v>
+        <v>22.13525222481821</v>
       </c>
       <c r="O3" t="n">
-        <v>4.711781272116433</v>
+        <v>4.704811603541444</v>
       </c>
       <c r="P3" t="n">
-        <v>406.9138172665465</v>
+        <v>406.9468223484778</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16111,28 +16191,28 @@
         <v>0.0733</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005384505530800342</v>
+        <v>0.004671822731991261</v>
       </c>
       <c r="J4" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K4" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L4" t="n">
-        <v>9.630364774537714e-05</v>
+        <v>7.331762034312739e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.237549845448654</v>
+        <v>3.227423745766686</v>
       </c>
       <c r="N4" t="n">
-        <v>15.75006392705328</v>
+        <v>15.67683903543094</v>
       </c>
       <c r="O4" t="n">
-        <v>3.968635020640382</v>
+        <v>3.959398822476834</v>
       </c>
       <c r="P4" t="n">
-        <v>406.9638782395835</v>
+        <v>406.971453764326</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16189,28 +16269,28 @@
         <v>0.0835</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0187371405995635</v>
+        <v>-0.01767561932636877</v>
       </c>
       <c r="J5" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K5" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001127025319579977</v>
+        <v>0.001014003545738995</v>
       </c>
       <c r="M5" t="n">
-        <v>3.136282266177778</v>
+        <v>3.127211881007026</v>
       </c>
       <c r="N5" t="n">
-        <v>16.28015184149083</v>
+        <v>16.21045473176695</v>
       </c>
       <c r="O5" t="n">
-        <v>4.034867016580699</v>
+        <v>4.026220899524386</v>
       </c>
       <c r="P5" t="n">
-        <v>405.0076525784138</v>
+        <v>404.9963161508836</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16267,28 +16347,28 @@
         <v>0.0956</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09648362459403864</v>
+        <v>-0.09763554502582943</v>
       </c>
       <c r="J6" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K6" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02682634695007957</v>
+        <v>0.02775624683254518</v>
       </c>
       <c r="M6" t="n">
-        <v>3.246185991751274</v>
+        <v>3.235605925027486</v>
       </c>
       <c r="N6" t="n">
-        <v>17.6689709081708</v>
+        <v>17.58556482327205</v>
       </c>
       <c r="O6" t="n">
-        <v>4.203447502725686</v>
+        <v>4.193514614648678</v>
       </c>
       <c r="P6" t="n">
-        <v>404.6172392782105</v>
+        <v>404.6295010423884</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16345,28 +16425,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1047264557680361</v>
+        <v>-0.1081211224557086</v>
       </c>
       <c r="J7" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K7" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03206498448987183</v>
+        <v>0.03437688449775567</v>
       </c>
       <c r="M7" t="n">
-        <v>3.438753556443084</v>
+        <v>3.4364143587111</v>
       </c>
       <c r="N7" t="n">
-        <v>17.32220638054403</v>
+        <v>17.29371196635069</v>
       </c>
       <c r="O7" t="n">
-        <v>4.161995480601106</v>
+        <v>4.158570904331281</v>
       </c>
       <c r="P7" t="n">
-        <v>413.4976484070829</v>
+        <v>413.5338011874715</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16404,7 +16484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H377"/>
+  <dimension ref="A1:H379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32241,6 +32321,90 @@
         </is>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>-36.764418602486785,175.14465767981244</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>-36.76468407030491,175.14543895629487</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>-36.76448774861637,175.14616942409765</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>-36.76418835867985,175.14689148557318</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>-36.76381922401103,175.14761404240983</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>-36.763336920359905,175.14826803494245</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:33+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>-36.764418602486785,175.14465767981244</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>-36.764660379414835,175.1454344353191</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>-36.764467681893144,175.14615853447106</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>-36.76416603706515,175.14687354615714</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>-36.763806553236435,175.14760182009314</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>-36.76331576755965,175.14824658005926</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0165/nzd0165.xlsx
+++ b/data/nzd0165/nzd0165.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H379"/>
+  <dimension ref="A1:H383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11808,6 +11808,126 @@
         <v>409.12</v>
       </c>
       <c r="H379" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>435.93</v>
+      </c>
+      <c r="C380" t="n">
+        <v>406.29</v>
+      </c>
+      <c r="D380" t="n">
+        <v>408.92</v>
+      </c>
+      <c r="E380" t="n">
+        <v>408.52</v>
+      </c>
+      <c r="F380" t="n">
+        <v>402.04</v>
+      </c>
+      <c r="G380" t="n">
+        <v>410.76</v>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>441.83</v>
+      </c>
+      <c r="C381" t="n">
+        <v>405.92</v>
+      </c>
+      <c r="D381" t="n">
+        <v>409.97</v>
+      </c>
+      <c r="E381" t="n">
+        <v>408.55</v>
+      </c>
+      <c r="F381" t="n">
+        <v>402.9</v>
+      </c>
+      <c r="G381" t="n">
+        <v>412.28</v>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>442.54</v>
+      </c>
+      <c r="C382" t="n">
+        <v>406.21</v>
+      </c>
+      <c r="D382" t="n">
+        <v>409.8</v>
+      </c>
+      <c r="E382" t="n">
+        <v>407.9</v>
+      </c>
+      <c r="F382" t="n">
+        <v>402.96</v>
+      </c>
+      <c r="G382" t="n">
+        <v>413.04</v>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>437.32</v>
+      </c>
+      <c r="C383" t="n">
+        <v>407.29</v>
+      </c>
+      <c r="D383" t="n">
+        <v>410.13</v>
+      </c>
+      <c r="E383" t="n">
+        <v>407.6</v>
+      </c>
+      <c r="F383" t="n">
+        <v>402.94</v>
+      </c>
+      <c r="G383" t="n">
+        <v>412.52</v>
+      </c>
+      <c r="H383" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11824,7 +11944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B404"/>
+  <dimension ref="A1:B408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15867,6 +15987,46 @@
       </c>
       <c r="B404" t="n">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>-0.84</v>
       </c>
     </row>
   </sheetData>
@@ -16035,28 +16195,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06872332554069469</v>
+        <v>0.09068216726082078</v>
       </c>
       <c r="J2" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="K2" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00873803109124105</v>
+        <v>0.01486702473498736</v>
       </c>
       <c r="M2" t="n">
-        <v>4.168686167600943</v>
+        <v>4.229734543780212</v>
       </c>
       <c r="N2" t="n">
-        <v>28.21689252068242</v>
+        <v>29.07791275089758</v>
       </c>
       <c r="O2" t="n">
-        <v>5.311957503659307</v>
+        <v>5.392393972151662</v>
       </c>
       <c r="P2" t="n">
-        <v>427.2881435665606</v>
+        <v>427.0524070237419</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16113,28 +16273,28 @@
         <v>0.0638</v>
       </c>
       <c r="I3" t="n">
-        <v>0.015284772461906</v>
+        <v>0.01331485256178401</v>
       </c>
       <c r="J3" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="K3" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005555435833860534</v>
+        <v>0.0004315132682901623</v>
       </c>
       <c r="M3" t="n">
-        <v>3.874622838800041</v>
+        <v>3.8443798029132</v>
       </c>
       <c r="N3" t="n">
-        <v>22.13525222481821</v>
+        <v>21.91491446115576</v>
       </c>
       <c r="O3" t="n">
-        <v>4.704811603541444</v>
+        <v>4.681336824151383</v>
       </c>
       <c r="P3" t="n">
-        <v>406.9468223484778</v>
+        <v>406.9679603925791</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16191,28 +16351,28 @@
         <v>0.0733</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004671822731991261</v>
+        <v>0.01023459759948523</v>
       </c>
       <c r="J4" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="K4" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="L4" t="n">
-        <v>7.331762034312739e-05</v>
+        <v>0.0003585601309488151</v>
       </c>
       <c r="M4" t="n">
-        <v>3.227423745766686</v>
+        <v>3.215706487192214</v>
       </c>
       <c r="N4" t="n">
-        <v>15.67683903543094</v>
+        <v>15.58376720710401</v>
       </c>
       <c r="O4" t="n">
-        <v>3.959398822476834</v>
+        <v>3.947628048221363</v>
       </c>
       <c r="P4" t="n">
-        <v>406.971453764326</v>
+        <v>406.9117293964477</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16269,28 +16429,28 @@
         <v>0.0835</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01767561932636877</v>
+        <v>-0.009969340015730058</v>
       </c>
       <c r="J5" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="K5" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001014003545738995</v>
+        <v>0.0003277970597379554</v>
       </c>
       <c r="M5" t="n">
-        <v>3.127211881007026</v>
+        <v>3.130310759510994</v>
       </c>
       <c r="N5" t="n">
-        <v>16.21045473176695</v>
+        <v>16.17461804572156</v>
       </c>
       <c r="O5" t="n">
-        <v>4.026220899524386</v>
+        <v>4.02176802485195</v>
       </c>
       <c r="P5" t="n">
-        <v>404.9963161508836</v>
+        <v>404.913599772222</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16347,28 +16507,28 @@
         <v>0.0956</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09763554502582943</v>
+        <v>-0.0962056720747156</v>
       </c>
       <c r="J6" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="K6" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02775624683254518</v>
+        <v>0.02759061952482855</v>
       </c>
       <c r="M6" t="n">
-        <v>3.235605925027486</v>
+        <v>3.207456380452197</v>
       </c>
       <c r="N6" t="n">
-        <v>17.58556482327205</v>
+        <v>17.40755186005179</v>
       </c>
       <c r="O6" t="n">
-        <v>4.193514614648678</v>
+        <v>4.172235834663686</v>
       </c>
       <c r="P6" t="n">
-        <v>404.6295010423884</v>
+        <v>404.6141443309236</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16425,28 +16585,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1081211224557086</v>
+        <v>-0.1049557811787588</v>
       </c>
       <c r="J7" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="K7" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03437688449775567</v>
+        <v>0.03315466079411566</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4364143587111</v>
+        <v>3.416069484255826</v>
       </c>
       <c r="N7" t="n">
-        <v>17.29371196635069</v>
+        <v>17.14248603986739</v>
       </c>
       <c r="O7" t="n">
-        <v>4.158570904331281</v>
+        <v>4.140348540867953</v>
       </c>
       <c r="P7" t="n">
-        <v>413.5338011874715</v>
+        <v>413.4998058607268</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16484,7 +16644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H379"/>
+  <dimension ref="A1:H383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32405,6 +32565,174 @@
         </is>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>-36.7643644525767,175.14465854828822</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>-36.76465663874795,175.1454337214811</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>-36.76445727692504,175.14615288800036</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>-36.76415423309138,175.14686405955496</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>-36.763805556658596,175.14760085878748</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>-36.76330431851744,175.14823496752018</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>-36.76431129376272,175.1446594008691</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>-36.764659934097345,175.14543435033838</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>-36.76444860611804,175.1461481826093</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>-36.764154006091864,175.14686387712032</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>-36.763799434823135,175.14759495362486</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>-36.7632937072089,175.1482242046822</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>-36.764304896685076,175.14465950346786</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>-36.764657351255934,175.14543385745026</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>-36.76445000996301,175.14614894443443</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>-36.7641589244144,175.14686782987087</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>-36.76379900771831,175.14759454163683</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>-36.76328840155422,175.1482188232643</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>-36.764351928720565,175.14465874915044</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>-36.76464773239818,175.14543202186718</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>-36.76444728485219,175.1461474655974</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>-36.76416119440935,175.1468696542174</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>-36.76379915008659,175.1475946789662</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>-36.763292031739034,175.148222505287</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0165/nzd0165.xlsx
+++ b/data/nzd0165/nzd0165.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H383"/>
+  <dimension ref="A1:H386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11928,6 +11928,96 @@
         <v>412.52</v>
       </c>
       <c r="H383" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:04:43+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>437.32</v>
+      </c>
+      <c r="C384" t="n">
+        <v>411.94</v>
+      </c>
+      <c r="D384" t="n">
+        <v>412.89</v>
+      </c>
+      <c r="E384" t="n">
+        <v>407.6</v>
+      </c>
+      <c r="F384" t="n">
+        <v>402.94</v>
+      </c>
+      <c r="G384" t="n">
+        <v>412.52</v>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>436.27</v>
+      </c>
+      <c r="C385" t="n">
+        <v>412.29</v>
+      </c>
+      <c r="D385" t="n">
+        <v>412.93</v>
+      </c>
+      <c r="E385" t="n">
+        <v>406.83</v>
+      </c>
+      <c r="F385" t="n">
+        <v>402.78</v>
+      </c>
+      <c r="G385" t="n">
+        <v>412.95</v>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>434.55</v>
+      </c>
+      <c r="C386" t="n">
+        <v>412.2</v>
+      </c>
+      <c r="D386" t="n">
+        <v>412.76</v>
+      </c>
+      <c r="E386" t="n">
+        <v>405.88</v>
+      </c>
+      <c r="F386" t="n">
+        <v>402.27</v>
+      </c>
+      <c r="G386" t="n">
+        <v>412.37</v>
+      </c>
+      <c r="H386" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11944,7 +12034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B408"/>
+  <dimension ref="A1:B411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16027,6 +16117,36 @@
       </c>
       <c r="B408" t="n">
         <v>-0.84</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>-0.89</v>
       </c>
     </row>
   </sheetData>
@@ -16195,28 +16315,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09068216726082078</v>
+        <v>0.1010291594402945</v>
       </c>
       <c r="J2" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K2" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01486702473498736</v>
+        <v>0.01848970898936575</v>
       </c>
       <c r="M2" t="n">
-        <v>4.229734543780212</v>
+        <v>4.24953849519237</v>
       </c>
       <c r="N2" t="n">
-        <v>29.07791275089758</v>
+        <v>29.19113931842811</v>
       </c>
       <c r="O2" t="n">
-        <v>5.392393972151662</v>
+        <v>5.402882500890438</v>
       </c>
       <c r="P2" t="n">
-        <v>427.0524070237419</v>
+        <v>426.9409671489501</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16273,28 +16393,28 @@
         <v>0.0638</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01331485256178401</v>
+        <v>0.0208916685416095</v>
       </c>
       <c r="J3" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K3" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004315132682901623</v>
+        <v>0.001071557375800003</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8443798029132</v>
+        <v>3.848573638329089</v>
       </c>
       <c r="N3" t="n">
-        <v>21.91491446115576</v>
+        <v>21.9208801408963</v>
       </c>
       <c r="O3" t="n">
-        <v>4.681336824151383</v>
+        <v>4.681973957733672</v>
       </c>
       <c r="P3" t="n">
-        <v>406.9679603925791</v>
+        <v>406.8863379476081</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16351,28 +16471,28 @@
         <v>0.0733</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01023459759948523</v>
+        <v>0.01915986056721806</v>
       </c>
       <c r="J4" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K4" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003585601309488151</v>
+        <v>0.001257554038434194</v>
       </c>
       <c r="M4" t="n">
-        <v>3.215706487192214</v>
+        <v>3.225499935155089</v>
       </c>
       <c r="N4" t="n">
-        <v>15.58376720710401</v>
+        <v>15.70740075697212</v>
       </c>
       <c r="O4" t="n">
-        <v>3.947628048221363</v>
+        <v>3.963256332483696</v>
       </c>
       <c r="P4" t="n">
-        <v>406.9117293964477</v>
+        <v>406.8155837804134</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16429,28 +16549,28 @@
         <v>0.0835</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.009969340015730058</v>
+        <v>-0.006635842977517669</v>
       </c>
       <c r="J5" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K5" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003277970597379554</v>
+        <v>0.000147453588805857</v>
       </c>
       <c r="M5" t="n">
-        <v>3.130310759510994</v>
+        <v>3.121356956575585</v>
       </c>
       <c r="N5" t="n">
-        <v>16.17461804572156</v>
+        <v>16.08664938259188</v>
       </c>
       <c r="O5" t="n">
-        <v>4.02176802485195</v>
+        <v>4.010816548109859</v>
       </c>
       <c r="P5" t="n">
-        <v>404.913599772222</v>
+        <v>404.8777035177562</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16507,28 +16627,28 @@
         <v>0.0956</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0962056720747156</v>
+        <v>-0.09525016542936941</v>
       </c>
       <c r="J6" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K6" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02759061952482855</v>
+        <v>0.02751567983102632</v>
       </c>
       <c r="M6" t="n">
-        <v>3.207456380452197</v>
+        <v>3.186239435757566</v>
       </c>
       <c r="N6" t="n">
-        <v>17.40755186005179</v>
+        <v>17.2753407400047</v>
       </c>
       <c r="O6" t="n">
-        <v>4.172235834663686</v>
+        <v>4.156361478505533</v>
       </c>
       <c r="P6" t="n">
-        <v>404.6141443309236</v>
+        <v>404.6038566791121</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16585,28 +16705,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1049557811787588</v>
+        <v>-0.1019599706554876</v>
       </c>
       <c r="J7" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K7" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03315466079411566</v>
+        <v>0.03182817815402283</v>
       </c>
       <c r="M7" t="n">
-        <v>3.416069484255826</v>
+        <v>3.404244201265403</v>
       </c>
       <c r="N7" t="n">
-        <v>17.14248603986739</v>
+        <v>17.03698913747637</v>
       </c>
       <c r="O7" t="n">
-        <v>4.140348540867953</v>
+        <v>4.127588780084126</v>
       </c>
       <c r="P7" t="n">
-        <v>413.4998058607268</v>
+        <v>413.4675356882435</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16644,7 +16764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H383"/>
+  <dimension ref="A1:H386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32733,6 +32853,132 @@
         </is>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:04:43+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>-36.764351928720565,175.14465874915044</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>-36.76460631787115,175.14542411866816</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>-36.764424493015454,175.1461350971466</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>-36.76416119440935,175.1468696542174</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>-36.76379915008659,175.1475946789662</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>-36.763292031739034,175.148222505287</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>-36.76436138918743,175.14465859741998</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>-36.764603200648644,175.1454235238041</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-36.764424162698965,175.14613491789376</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>-36.7641670207296,175.14687433670744</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>-36.763800289032744,175.147595777601</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>-36.76328902985545,175.14821946053746</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>-36.764376886333125,175.1446583488711</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>-36.764604002220146,175.14542367676916</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>-36.764425566544034,175.1461356797184</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>-36.7641742090465,175.14688011380653</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>-36.76380391942357,175.14759927949973</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>-36.763293078907694,175.148223567409</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
